--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE28746A-87E2-43B7-9225-208D84923900}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF77AA9-2C65-46F9-BEA6-C50C6918A081}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="11,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="14,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,42 +31,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>Симферополь</t>
+    <t>16,09,26</t>
   </si>
   <si>
-    <t>КСК</t>
+    <t>ЛП</t>
   </si>
   <si>
-    <t>Луганск</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>НВ</t>
-  </si>
-  <si>
-    <t>Донецк</t>
-  </si>
-  <si>
-    <t>13,09,26</t>
-  </si>
-  <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
-    <t>14,09,26</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>15,09,26</t>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -107,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -242,61 +218,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -309,24 +236,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -336,15 +245,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -357,16 +257,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -751,400 +642,83 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="22.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="11">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3">
-        <v>15423.2</v>
-      </c>
-      <c r="G1" s="4">
-        <v>4.1666666666666664E-2</v>
+      <c r="F1" s="6">
+        <v>4197.7699999999995</v>
+      </c>
+      <c r="G1" s="7">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="12"/>
+      <c r="B2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="F2" s="9">
+        <v>2167.4700000000003</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="7">
-        <v>17751.039999999997</v>
-      </c>
-      <c r="G2" s="8">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="24">
-        <v>3</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="16">
-        <v>10686.22</v>
-      </c>
-      <c r="G3" s="17">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="25"/>
-      <c r="B4" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="19">
-        <v>2259.3000000000002</v>
-      </c>
-      <c r="G4" s="20">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26"/>
-      <c r="B5" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="22">
-        <v>4914</v>
-      </c>
-      <c r="G5" s="23">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="27">
-        <v>4</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="10">
-        <v>9525.1799999999985</v>
-      </c>
-      <c r="G6" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="13">
-        <v>8393.86</v>
-      </c>
-      <c r="G7" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3">
-        <v>17593.480000000003</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="F3" s="3">
+        <v>17604.599999999999</v>
+      </c>
+      <c r="G3" s="4">
         <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>6</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="7">
-        <v>17815.55</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="24">
-        <v>7</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="16">
-        <v>6440.84</v>
-      </c>
-      <c r="G10" s="17">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="22">
-        <v>6430.28</v>
-      </c>
-      <c r="G11" s="23">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="7">
-        <v>15627.560000000001</v>
-      </c>
-      <c r="G12" s="8">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>18819.259999999998</v>
-      </c>
-      <c r="G13" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="7">
-        <v>5549.28</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3">
-        <v>17410.560000000001</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="27">
-        <v>12</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="10">
-        <v>10851.199999999999</v>
-      </c>
-      <c r="G16" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="13">
-        <v>3746.52</v>
-      </c>
-      <c r="G17" s="14">
-        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A16:A17"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF77AA9-2C65-46F9-BEA6-C50C6918A081}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1671D4-1686-4F1B-94E1-FB023F4CFD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="14,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="15,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,12 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>16,09,26</t>
   </si>
   <si>
     <t>ЛП</t>
@@ -44,11 +35,17 @@
   <si>
     <t>Сочи</t>
   </si>
+  <si>
+    <t>17,09,26</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -83,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -136,93 +133,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,29 +151,23 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -642,84 +551,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="11">
+    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6">
+        <v>18.300999999999998</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="F1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="7">
+        <v>18438.29</v>
+      </c>
+      <c r="H1" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="6">
-        <v>4197.7699999999995</v>
-      </c>
-      <c r="G1" s="7">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="9">
-        <v>2167.4700000000003</v>
-      </c>
-      <c r="G2" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="G2" s="3">
         <v>17604.599999999999</v>
       </c>
-      <c r="G3" s="4">
+      <c r="H2" s="4">
         <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1671D4-1686-4F1B-94E1-FB023F4CFD00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DAD9F0-8156-4351-B615-882A6A3BB5DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="15,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="16,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="11">
   <si>
     <t>КИ</t>
   </si>
@@ -36,16 +42,34 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>17,09,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>18,09,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>19,09,26</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -80,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -133,11 +157,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -154,20 +297,50 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -551,65 +724,219 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="6">
-        <v>18.300999999999998</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>1</v>
+      <c r="D1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="6">
+        <v>17519.439999999999</v>
       </c>
       <c r="G1" s="7">
-        <v>18438.29</v>
-      </c>
-      <c r="H1" s="8">
-        <v>0.41666666666666669</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3">
+        <v>17012.7</v>
+      </c>
+      <c r="G2" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="9">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="11">
+        <v>10186.780000000001</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="15">
+        <v>6172.44</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3">
+        <v>19045.059999999998</v>
+      </c>
+      <c r="G5" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C6" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="3">
-        <v>17604.599999999999</v>
-      </c>
-      <c r="H2" s="4">
+      <c r="F6" s="11">
+        <v>810</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="19">
+        <v>1907.4600000000003</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="15">
+        <v>15001</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="3">
+        <v>17809.12</v>
+      </c>
+      <c r="G9" s="4">
         <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A6:A8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DAD9F0-8156-4351-B615-882A6A3BB5DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB767208-754A-4D2C-8355-D6D6D06521A8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="16,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="17,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="13">
   <si>
     <t>КИ</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Симферополь</t>
   </si>
   <si>
-    <t>18,09,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
@@ -64,13 +61,25 @@
   </si>
   <si>
     <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>20,09,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -82,6 +91,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -280,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -306,9 +322,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -318,9 +331,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -330,9 +340,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -340,6 +347,48 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -724,11 +773,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -739,16 +788,16 @@
         <v>3</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>5</v>
-      </c>
       <c r="F1" s="6">
-        <v>17519.439999999999</v>
+        <v>14405.88</v>
       </c>
       <c r="G1" s="7">
         <v>4.1666666666666664E-2</v>
@@ -759,183 +808,334 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="3">
-        <v>17012.7</v>
+        <v>13048.8</v>
       </c>
       <c r="G2" s="4">
-        <v>8.3333333333333329E-2</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="9">
+      <c r="A3" s="18">
         <v>3</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10">
+        <v>998.4</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="20"/>
+      <c r="B4" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="16">
+        <v>8886.4399999999987</v>
+      </c>
+      <c r="G4" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="20"/>
+      <c r="B5" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="16">
+        <v>504</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="20"/>
+      <c r="B6" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="16">
+        <v>4937.8600000000006</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
+      <c r="B7" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="16">
+        <v>3396.4500000000003</v>
+      </c>
+      <c r="G7" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
+      <c r="B8" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="16">
+        <v>2496</v>
+      </c>
+      <c r="G8" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13">
+        <v>630</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="24">
+        <v>4</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C10" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F10" s="26">
+        <v>17019.879999999997</v>
+      </c>
+      <c r="G10" s="27">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="28"/>
+      <c r="B11" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="30">
+        <v>1811.24</v>
+      </c>
+      <c r="G11" s="31">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="18">
         <v>5</v>
       </c>
-      <c r="F3" s="11">
-        <v>10186.780000000001</v>
-      </c>
-      <c r="G3" s="12">
+      <c r="B12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="10">
+        <v>9325.31</v>
+      </c>
+      <c r="G12" s="11">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="15" t="s">
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19"/>
+      <c r="B13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="13">
+        <v>8606.24</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="24">
         <v>6</v>
       </c>
-      <c r="F4" s="15">
-        <v>6172.44</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B14" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="26">
+        <v>7930.4400000000014</v>
+      </c>
+      <c r="G14" s="27">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="28"/>
+      <c r="B15" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="30">
+        <v>9749.8799999999974</v>
+      </c>
+      <c r="G15" s="31">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <v>7</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="B16" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="3">
-        <v>19045.059999999998</v>
-      </c>
-      <c r="G5" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="11">
-        <v>810</v>
-      </c>
-      <c r="G6" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="19">
-        <v>1907.4600000000003</v>
-      </c>
-      <c r="G7" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="15">
-        <v>15001</v>
-      </c>
-      <c r="G8" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="3">
-        <v>17809.12</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.45833333333333331</v>
+      <c r="F16" s="6">
+        <v>17671.72</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A6:A8"/>
+  <mergeCells count="4">
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB767208-754A-4D2C-8355-D6D6D06521A8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B06E34-A254-4062-B00A-D5D967417993}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="17,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="18,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,15 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="12">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
   </si>
   <si>
     <t>Симферополь</t>
@@ -49,9 +43,6 @@
   </si>
   <si>
     <t>НВ</t>
-  </si>
-  <si>
-    <t>19,09,26</t>
   </si>
   <si>
     <t>Донецк</t>
@@ -66,20 +57,23 @@
     <t>ЗПФ</t>
   </si>
   <si>
-    <t>20,09,26</t>
+    <t>Бердянск</t>
   </si>
   <si>
-    <t>Бердянск</t>
+    <t>21,09,26</t>
+  </si>
+  <si>
+    <t>Горняк</t>
+  </si>
+  <si>
+    <t>22,09,26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -91,13 +85,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -296,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -340,36 +327,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -379,9 +336,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -389,6 +343,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -773,369 +751,355 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3">
+        <v>17603.78</v>
+      </c>
+      <c r="G1" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="23">
+        <v>2</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="F2" s="10">
+        <v>8078.6400000000012</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="24"/>
+      <c r="B3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="13">
+        <v>5692.6</v>
+      </c>
+      <c r="G3" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>16838.939999999999</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="6">
+        <v>15191.000000000004</v>
+      </c>
+      <c r="G5" s="7">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="21">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="16">
+        <v>6041.5199999999995</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="25"/>
+      <c r="B7" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="27">
+        <v>4833.12</v>
+      </c>
+      <c r="G7" s="28">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22"/>
+      <c r="B8" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="19">
+        <v>2437.6799999999998</v>
+      </c>
+      <c r="G8" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="23">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="C9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="10">
+        <v>9354.24</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="B10" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6">
-        <v>14405.88</v>
-      </c>
-      <c r="G1" s="7">
+      <c r="C10" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="13">
+        <v>5099.5200000000004</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>19177.359999999997</v>
+      </c>
+      <c r="G11" s="4">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6">
+        <v>17741.260000000002</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>16888.060000000001</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="F14" s="6">
+        <v>18284.600000000002</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="3">
-        <v>13048.8</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>11188.800000000001</v>
+      </c>
+      <c r="G15" s="4">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
-        <v>3</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10">
-        <v>998.4</v>
-      </c>
-      <c r="G3" s="11">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="20"/>
-      <c r="B4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="16">
-        <v>8886.4399999999987</v>
-      </c>
-      <c r="G4" s="17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="20"/>
-      <c r="B5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="16">
-        <v>504</v>
-      </c>
-      <c r="G5" s="17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="20"/>
-      <c r="B6" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="16">
-        <v>4937.8600000000006</v>
-      </c>
-      <c r="G6" s="17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="16">
-        <v>3396.4500000000003</v>
-      </c>
-      <c r="G7" s="17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="16">
-        <v>2496</v>
-      </c>
-      <c r="G8" s="17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19"/>
-      <c r="B9" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="13">
-        <v>630</v>
-      </c>
-      <c r="G9" s="14">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="24">
-        <v>4</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="26">
-        <v>17019.879999999997</v>
-      </c>
-      <c r="G10" s="27">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="30">
-        <v>1811.24</v>
-      </c>
-      <c r="G11" s="31">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="18">
-        <v>5</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="10">
-        <v>9325.31</v>
-      </c>
-      <c r="G12" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="13">
-        <v>8606.24</v>
-      </c>
-      <c r="G13" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="24">
-        <v>6</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="26">
-        <v>7930.4400000000014</v>
-      </c>
-      <c r="G14" s="27">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="30">
-        <v>9749.8799999999974</v>
-      </c>
-      <c r="G15" s="31">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>7</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="6">
-        <v>17671.72</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
+  <mergeCells count="3">
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B06E34-A254-4062-B00A-D5D967417993}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4686794-08F6-4574-ADC9-A4D2732E6C05}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="18,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="21,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,42 +31,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>Симферополь</t>
+    <t>23,09,26</t>
   </si>
   <si>
-    <t>КСК</t>
+    <t>ЛП</t>
   </si>
   <si>
-    <t>НВ</t>
-  </si>
-  <si>
-    <t>Донецк</t>
-  </si>
-  <si>
-    <t>Луганск</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
-    <t>21,09,26</t>
-  </si>
-  <si>
-    <t>Горняк</t>
-  </si>
-  <si>
-    <t>22,09,26</t>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -283,20 +259,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -309,24 +273,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -345,21 +291,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -367,6 +298,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -751,355 +691,124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3">
-        <v>17603.78</v>
-      </c>
-      <c r="G1" s="4">
-        <v>4.1666666666666664E-2</v>
+      <c r="F1" s="2">
+        <v>17604.599999999999</v>
+      </c>
+      <c r="G1" s="3">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="23">
+      <c r="A2" s="14">
         <v>2</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="10" t="s">
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="D2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2042.1699999999998</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="15"/>
+      <c r="B3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="10">
-        <v>8078.6400000000012</v>
-      </c>
-      <c r="G2" s="11">
-        <v>0.41666666666666669</v>
+      <c r="C3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="12">
+        <v>7295.6399999999994</v>
+      </c>
+      <c r="G3" s="13">
+        <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24"/>
-      <c r="B3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="13" t="s">
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="13">
-        <v>5692.6</v>
-      </c>
-      <c r="G3" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3">
-        <v>16838.939999999999</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="D4" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="12">
+        <v>5506.8</v>
+      </c>
+      <c r="G4" s="13">
         <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
+      <c r="A5" s="16"/>
       <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F5" s="6">
-        <v>15191.000000000004</v>
-      </c>
-      <c r="G5" s="7">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="21">
-        <v>5</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="16">
-        <v>6041.5199999999995</v>
-      </c>
-      <c r="G6" s="17">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="27">
-        <v>4833.12</v>
-      </c>
-      <c r="G7" s="28">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
-      <c r="B8" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="19">
-        <v>2437.6799999999998</v>
-      </c>
-      <c r="G8" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="23">
-        <v>6</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="10">
-        <v>9354.24</v>
-      </c>
-      <c r="G9" s="11">
+      <c r="F5" s="9">
+        <v>3502.2</v>
+      </c>
+      <c r="G5" s="10">
         <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="13">
-        <v>5099.5200000000004</v>
-      </c>
-      <c r="G10" s="14">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>19177.359999999997</v>
-      </c>
-      <c r="G11" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>8</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="6">
-        <v>17741.260000000002</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="3">
-        <v>16888.060000000001</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>10</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6">
-        <v>18284.600000000002</v>
-      </c>
-      <c r="G14" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3">
-        <v>11188.800000000001</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A2:A3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4686794-08F6-4574-ADC9-A4D2732E6C05}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3621457A-7D5B-440A-B018-483915D95924}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="21,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="22,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,18 +31,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>23,09,26</t>
   </si>
   <si>
     <t>ЛП</t>
   </si>
   <si>
     <t>Сочи</t>
+  </si>
+  <si>
+    <t>24,09,26</t>
   </si>
 </sst>
 </file>
@@ -83,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -136,130 +136,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -273,40 +154,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -691,10 +548,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -702,114 +559,48 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="F1" s="2">
-        <v>17604.599999999999</v>
+        <v>18146.96</v>
       </c>
       <c r="G1" s="3">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="14">
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6">
-        <v>2042.1699999999998</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="15"/>
-      <c r="B3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="12">
-        <v>7295.6399999999994</v>
-      </c>
-      <c r="G3" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="15"/>
-      <c r="B4" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="12">
-        <v>5506.8</v>
-      </c>
-      <c r="G4" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="9">
-        <v>3502.2</v>
-      </c>
-      <c r="G5" s="10">
+      <c r="F2" s="7">
+        <v>18098.380000000005</v>
+      </c>
+      <c r="G2" s="8">
         <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A5"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3621457A-7D5B-440A-B018-483915D95924}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C5BF11-C2A2-4A1F-89F1-B75D1EA656E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="22,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="23,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="12">
   <si>
     <t>КИ</t>
   </si>
@@ -42,7 +36,31 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>24,09,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>25,09,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>26,09,26</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
   </si>
 </sst>
 </file>
@@ -83,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -136,11 +154,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -164,6 +301,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,10 +757,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -559,22 +769,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F1" s="2">
-        <v>18146.96</v>
+        <v>17648.800000000003</v>
       </c>
       <c r="G1" s="3">
-        <v>0.41666666666666669</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -582,25 +792,340 @@
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="7">
+        <v>17019</v>
+      </c>
+      <c r="G2" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>12383.240000000002</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="7">
+        <v>11730.6</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>17716.34</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="7">
+        <v>17700.18</v>
+      </c>
+      <c r="G6" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="9">
+        <v>7</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="11">
+        <v>917.6400000000001</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="15">
+        <v>8135.2799999999988</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="17"/>
+      <c r="B9" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="19">
+        <v>8702.58</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="21">
+        <v>8</v>
+      </c>
+      <c r="B10" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="C10" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="7">
-        <v>18098.380000000005</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="F10" s="23">
+        <v>920.10000000000014</v>
+      </c>
+      <c r="G10" s="24">
         <v>0.45833333333333331</v>
       </c>
     </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="27">
+        <v>2218.1999999999998</v>
+      </c>
+      <c r="G11" s="28">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="31">
+        <v>10736.63</v>
+      </c>
+      <c r="G12" s="32">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>18018.059999999998</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="21">
+        <v>10</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="23">
+        <v>2503.7999999999997</v>
+      </c>
+      <c r="G14" s="24">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="25"/>
+      <c r="B15" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="27">
+        <v>5722.3</v>
+      </c>
+      <c r="G15" s="28">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="29"/>
+      <c r="B16" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="31">
+        <v>9429.26</v>
+      </c>
+      <c r="G16" s="32">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A14:A16"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C5BF11-C2A2-4A1F-89F1-B75D1EA656E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11CE9CFD-C7B5-49AB-BCD1-97EAE7F32FE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="23,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="24,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,23 +31,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
-  </si>
-  <si>
     <t>Симферополь</t>
   </si>
   <si>
-    <t>25,09,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
@@ -57,10 +54,16 @@
     <t>26,09,26</t>
   </si>
   <si>
-    <t>Луганск</t>
-  </si>
-  <si>
     <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>27,09,26</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
   </si>
 </sst>
 </file>
@@ -101,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -192,43 +195,6 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -277,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,21 +257,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -315,9 +266,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -327,21 +275,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -351,9 +284,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -363,16 +293,16 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -757,11 +687,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -769,362 +699,184 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F1" s="2">
-        <v>17648.800000000003</v>
+        <v>13975.440000000002</v>
       </c>
       <c r="G1" s="3">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="19">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="7">
-        <v>17019</v>
-      </c>
-      <c r="G2" s="8">
-        <v>8.3333333333333329E-2</v>
+      <c r="D2" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="12">
+        <v>15524.040000000003</v>
+      </c>
+      <c r="G2" s="13">
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3" s="20"/>
+      <c r="B3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="15">
+        <v>2391.2400000000002</v>
+      </c>
+      <c r="G3" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="2">
-        <v>12383.240000000002</v>
-      </c>
-      <c r="G3" s="3">
+      <c r="E4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="6">
+        <v>13937.400000000001</v>
+      </c>
+      <c r="G4" s="7">
         <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>4</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="7">
-        <v>11730.6</v>
-      </c>
-      <c r="G4" s="8">
-        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5" s="18"/>
+      <c r="B5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="F5" s="9">
+        <v>3941.5599999999995</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="19">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="12">
+        <v>12165.599999999999</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="15">
+        <v>5486.38</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="2">
-        <v>17716.34</v>
-      </c>
-      <c r="G5" s="3">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>6</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="7">
-        <v>17700.18</v>
-      </c>
-      <c r="G6" s="8">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
-        <v>7</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="11">
-        <v>917.6400000000001</v>
-      </c>
-      <c r="G7" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="15">
-        <v>8135.2799999999988</v>
-      </c>
-      <c r="G8" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="19">
-        <v>8702.58</v>
-      </c>
-      <c r="G9" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="21">
-        <v>8</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="23">
-        <v>920.10000000000014</v>
-      </c>
-      <c r="G10" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="27">
-        <v>2218.1999999999998</v>
-      </c>
-      <c r="G11" s="28">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="31">
-        <v>10736.63</v>
-      </c>
-      <c r="G12" s="32">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2">
-        <v>18018.059999999998</v>
-      </c>
-      <c r="G13" s="3">
+      <c r="F8" s="2">
+        <v>17596.78</v>
+      </c>
+      <c r="G8" s="3">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="21">
-        <v>10</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="23">
-        <v>2503.7999999999997</v>
-      </c>
-      <c r="G14" s="24">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="25"/>
-      <c r="B15" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="27">
-        <v>5722.3</v>
-      </c>
-      <c r="G15" s="28">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="29"/>
-      <c r="B16" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="31">
-        <v>9429.26</v>
-      </c>
-      <c r="G16" s="32">
-        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11CE9CFD-C7B5-49AB-BCD1-97EAE7F32FE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10DAE6C-76F6-414B-85FB-0CA3AB6B35C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="24,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="25,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="15">
   <si>
     <t>КИ</t>
   </si>
@@ -51,9 +51,6 @@
     <t>НВ</t>
   </si>
   <si>
-    <t>26,09,26</t>
-  </si>
-  <si>
     <t>Мелитополь</t>
   </si>
   <si>
@@ -64,6 +61,21 @@
   </si>
   <si>
     <t>Бердянск</t>
+  </si>
+  <si>
+    <t>28,09,26</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>29,09,26</t>
+  </si>
+  <si>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -243,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -293,16 +305,28 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -687,10 +711,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -699,184 +723,322 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2">
+        <v>3755.04</v>
+      </c>
+      <c r="G1" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21">
+        <v>2</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C2" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="23">
+        <v>14704.919999999998</v>
+      </c>
+      <c r="G2" s="24">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>17766.599999999999</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21">
+        <v>4</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="23">
+        <v>17258.82</v>
+      </c>
+      <c r="G4" s="24">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>16703.239999999998</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="17">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2">
-        <v>13975.440000000002</v>
-      </c>
-      <c r="G1" s="3">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="19">
-        <v>2</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="12">
-        <v>15524.040000000003</v>
-      </c>
-      <c r="G2" s="13">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="15">
-        <v>2391.2400000000002</v>
-      </c>
-      <c r="G3" s="16">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="17">
+      <c r="B6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="C6" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="6">
-        <v>13937.400000000001</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="F6" s="12">
+        <v>11419.76</v>
+      </c>
+      <c r="G6" s="13">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="9">
-        <v>3941.5599999999995</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18"/>
+      <c r="B7" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="12">
-        <v>12165.599999999999</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
-      <c r="B7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>10</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>8</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="15">
-        <v>5486.38</v>
+        <v>1982.72</v>
       </c>
       <c r="G7" s="16">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>17744.580000000002</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="17">
         <v>8</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="B9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="2">
-        <v>17596.78</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="F9" s="12">
+        <v>11063.150000000001</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18"/>
+      <c r="B10" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="15">
+        <v>4115.1400000000003</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2">
+        <v>16905.979999999996</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21">
+        <v>10</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="23">
+        <v>18187.610000000004</v>
+      </c>
+      <c r="G12" s="24">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="19">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="6">
+        <v>2750.16</v>
+      </c>
+      <c r="G13" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="9">
+        <v>9550.6400000000012</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A13:A14"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A9:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10DAE6C-76F6-414B-85FB-0CA3AB6B35C5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D1679C-6881-40B1-BB86-0CB97CC87BF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="25,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="29,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,51 +31,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>Симферополь</t>
-  </si>
-  <si>
-    <t>КСК</t>
-  </si>
-  <si>
-    <t>Донецк</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>НВ</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>27,09,26</t>
-  </si>
-  <si>
-    <t>Мариуполь</t>
-  </si>
-  <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
-    <t>28,09,26</t>
-  </si>
-  <si>
-    <t>Луганск</t>
-  </si>
-  <si>
-    <t>29,09,26</t>
   </si>
   <si>
     <t>ЛП</t>
   </si>
   <si>
     <t>Сочи</t>
+  </si>
+  <si>
+    <t>01,10,26</t>
   </si>
 </sst>
 </file>
@@ -96,7 +63,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,14 +76,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -169,154 +130,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -711,335 +530,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="2">
-        <v>3755.04</v>
-      </c>
-      <c r="G1" s="3">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21">
-        <v>2</v>
-      </c>
-      <c r="B2" s="22" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="23">
-        <v>14704.919999999998</v>
-      </c>
-      <c r="G2" s="24">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2">
-        <v>17766.599999999999</v>
-      </c>
-      <c r="G3" s="3">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21">
-        <v>4</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="23">
-        <v>17258.82</v>
-      </c>
-      <c r="G4" s="24">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>5</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2">
-        <v>16703.239999999998</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="17">
-        <v>6</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="12">
-        <v>11419.76</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
-      <c r="B7" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="15">
-        <v>1982.72</v>
-      </c>
-      <c r="G7" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2">
-        <v>17744.580000000002</v>
-      </c>
-      <c r="G8" s="3">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="17">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="12">
-        <v>11063.150000000001</v>
-      </c>
-      <c r="G9" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="15">
-        <v>4115.1400000000003</v>
-      </c>
-      <c r="G10" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="2">
-        <v>16905.979999999996</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21">
-        <v>10</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="23">
-        <v>18187.610000000004</v>
-      </c>
-      <c r="G12" s="24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="19">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="6">
-        <v>2750.16</v>
-      </c>
-      <c r="G13" s="7">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
-      <c r="B14" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="9">
-        <v>9550.6400000000012</v>
-      </c>
-      <c r="G14" s="10">
+      <c r="F1" s="3">
+        <v>18138.23</v>
+      </c>
+      <c r="G1" s="4">
         <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A9:A10"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D1679C-6881-40B1-BB86-0CB97CC87BF8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EF0AB2-6C38-427A-9E5F-52B3E34178D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="29,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="30,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30,09,26'!$A$1:$G$13</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,18 +28,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="12">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
-  </si>
-  <si>
-    <t>01,10,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>02,10,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>03,10,26</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
@@ -63,7 +84,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -76,8 +97,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -130,11 +157,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -146,6 +292,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -530,36 +748,287 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="7">
+        <v>17700.500000000004</v>
+      </c>
+      <c r="G2" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F3" s="3">
+        <v>17119.800000000003</v>
+      </c>
+      <c r="G3" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="24">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="10">
+        <v>4639.88</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="25"/>
+      <c r="B5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="13">
+        <v>5615.6400000000012</v>
+      </c>
+      <c r="G5" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26"/>
+      <c r="B6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="16">
+        <v>5727.1200000000008</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3">
-        <v>18138.23</v>
-      </c>
-      <c r="G1" s="4">
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3">
+        <v>14672.52</v>
+      </c>
+      <c r="G7" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7">
+        <v>17889.14</v>
+      </c>
+      <c r="G8" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="27">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="19">
+        <v>14923.7</v>
+      </c>
+      <c r="G9" s="20">
         <v>0.41666666666666669</v>
       </c>
     </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="28"/>
+      <c r="B10" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="22">
+        <v>2809.78</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="24">
+        <v>7</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="10">
+        <v>1075.04</v>
+      </c>
+      <c r="G11" s="11">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="25"/>
+      <c r="B12" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" s="13">
+        <v>7423.5599999999995</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="16">
+        <v>9340.3799999999992</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G13" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}"/>
+  <mergeCells count="3">
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,25 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EF0AB2-6C38-427A-9E5F-52B3E34178D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E9803D-7CF5-4CCC-B931-395E1FBCF579}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="30,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="01,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'30,09,26'!$A$1:$G$13</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="9">
   <si>
     <t>КИ</t>
   </si>
@@ -36,25 +39,10 @@
     <t>Симферополь</t>
   </si>
   <si>
-    <t>02,10,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
     <t>НВ</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>Мариуполь</t>
   </si>
   <si>
     <t>03,10,26</t>
@@ -63,7 +51,13 @@
     <t>Донецк</t>
   </si>
   <si>
-    <t>Луганск</t>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>04,10,26</t>
+  </si>
+  <si>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -280,20 +274,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -315,15 +297,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -351,19 +324,28 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -748,286 +730,215 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="20">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="7">
-        <v>17700.500000000004</v>
-      </c>
-      <c r="G2" s="8">
-        <v>4.1666666666666664E-2</v>
+      <c r="D1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="12">
+        <v>4163.92</v>
+      </c>
+      <c r="G1" s="13">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="21"/>
+      <c r="B2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="3">
-        <v>17119.800000000003</v>
-      </c>
-      <c r="G3" s="4">
-        <v>8.3333333333333329E-2</v>
+      <c r="D2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="18">
+        <v>6222.5400000000009</v>
+      </c>
+      <c r="G2" s="19">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="24">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="21"/>
+      <c r="B3" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="E3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="10">
-        <v>4639.88</v>
-      </c>
-      <c r="G4" s="11">
-        <v>0.41666666666666669</v>
+      <c r="F3" s="18">
+        <v>5593.7000000000007</v>
+      </c>
+      <c r="G3" s="19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="22"/>
+      <c r="B4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="15">
+        <v>1846.2</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="25"/>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="23">
+        <v>2</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="13">
-        <v>5615.6400000000012</v>
-      </c>
-      <c r="G5" s="14">
-        <v>0.41666666666666669</v>
+      <c r="F5" s="6">
+        <v>15933.300000000001</v>
+      </c>
+      <c r="G5" s="7">
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="A6" s="24"/>
+      <c r="B6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="9">
+        <v>2066.52</v>
+      </c>
+      <c r="G6" s="10">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="20">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="16">
-        <v>5727.1200000000008</v>
-      </c>
-      <c r="G6" s="17">
+      <c r="C7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="12">
+        <v>2218.1999999999998</v>
+      </c>
+      <c r="G7" s="13">
         <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3">
-        <v>14672.52</v>
-      </c>
-      <c r="G7" s="4">
-        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="22"/>
+      <c r="B8" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="15">
+        <v>15542.44</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="7">
-        <v>17889.14</v>
-      </c>
-      <c r="G8" s="8">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="27">
-        <v>6</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="19">
-        <v>14923.7</v>
-      </c>
-      <c r="G9" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
-      <c r="B10" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="22">
-        <v>2809.78</v>
-      </c>
-      <c r="G10" s="23">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="24">
+      <c r="D9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="10">
-        <v>1075.04</v>
-      </c>
-      <c r="G11" s="11">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="25"/>
-      <c r="B12" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" s="13">
-        <v>7423.5599999999995</v>
-      </c>
-      <c r="G12" s="14">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26"/>
-      <c r="B13" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="16">
-        <v>9340.3799999999992</v>
-      </c>
-      <c r="G13" s="17">
+      <c r="E9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>17098.8</v>
+      </c>
+      <c r="G9" s="4">
         <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}"/>
   <mergeCells count="3">
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E9803D-7CF5-4CCC-B931-395E1FBCF579}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C048878-DF7A-4502-B636-E280A55E073A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="01,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="02,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'02,10,26'!$A$1:$G$17</definedName>
+  </definedNames>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="12">
   <si>
     <t>КИ</t>
   </si>
@@ -45,19 +48,28 @@
     <t>НВ</t>
   </si>
   <si>
-    <t>03,10,26</t>
-  </si>
-  <si>
     <t>Донецк</t>
   </si>
   <si>
-    <t>ЛП</t>
+    <t>05,10,26</t>
   </si>
   <si>
-    <t>04,10,26</t>
+    <t>ЗПФ</t>
   </si>
   <si>
-    <t>Сочи</t>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>06,10,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
   </si>
 </sst>
 </file>
@@ -274,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -324,28 +336,40 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -730,215 +754,378 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.5703125" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="20">
+    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="19">
+        <v>17716.500000000004</v>
+      </c>
+      <c r="G2" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>15004.08</v>
+      </c>
+      <c r="G3" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="27">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="12">
+        <v>12474.890000000003</v>
+      </c>
+      <c r="G4" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="28"/>
+      <c r="B5" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="15">
+        <v>2770.3900000000003</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3">
+        <v>17039.13</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="27">
+        <v>5</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="C7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="12">
-        <v>4163.92</v>
-      </c>
-      <c r="G1" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="21"/>
-      <c r="B2" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="18">
-        <v>6222.5400000000009</v>
-      </c>
-      <c r="G2" s="19">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
-      <c r="B3" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="18">
-        <v>5593.7000000000007</v>
-      </c>
-      <c r="G3" s="19">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="15">
-        <v>1846.2</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="23">
-        <v>2</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="6">
-        <v>15933.300000000001</v>
-      </c>
-      <c r="G5" s="7">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="9">
-        <v>2066.52</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="20">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>7</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="12">
-        <v>2218.1999999999998</v>
+        <v>7528.88</v>
       </c>
       <c r="G7" s="13">
         <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>5</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>7</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>3</v>
       </c>
       <c r="F8" s="15">
-        <v>15542.44</v>
+        <v>5779.5199999999995</v>
       </c>
       <c r="G8" s="16">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="24">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="6">
+        <v>7641.4800000000005</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26"/>
+      <c r="B10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="9">
+        <v>5804.4</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>7</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="19">
+        <v>17798.7</v>
+      </c>
+      <c r="G11" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="24">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6">
+        <v>5082.3600000000006</v>
+      </c>
+      <c r="G12" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="25"/>
+      <c r="B13" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="22">
+        <v>4000.5099999999998</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26"/>
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="9">
+        <v>5923.8099999999995</v>
+      </c>
+      <c r="G14" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>9</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="19">
+        <v>17023.750000000004</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="24">
+        <v>10</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="6">
+        <v>6638.9600000000009</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="26"/>
+      <c r="B17" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>17098.8</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.45833333333333331</v>
+      <c r="C17" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F17" s="9">
+        <v>7188.24</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="A5:A6"/>
+  <autoFilter ref="A1:G17" xr:uid="{52EB17F6-0A5C-41DF-9FE2-99FF24B9BFC0}"/>
+  <mergeCells count="5">
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A4:A5"/>
     <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{891EEBAB-6F58-4D97-AE37-04B4CF469DBD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D4D520-27EC-4698-A208-66221AE4ABBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="05,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="06,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,12 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>07,10,26</t>
   </si>
   <si>
     <t>ЛП</t>
@@ -44,11 +41,17 @@
   <si>
     <t>Сочи</t>
   </si>
+  <si>
+    <t>08,10,26</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -63,7 +66,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -76,8 +79,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -95,20 +104,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -117,27 +113,14 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -145,25 +128,14 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -171,30 +143,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -579,60 +557,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="7">
+    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3">
+        <v>18.061</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="4">
+        <v>18200.600000000006</v>
+      </c>
+      <c r="H1" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="8">
+        <v>18.026</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G2" s="9">
+        <v>18150.86</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2">
-        <v>2960.6099999999997</v>
-      </c>
-      <c r="G1" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="4" t="s">
+      <c r="C3" s="3">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="5">
-        <v>9778.23</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="G3" s="4">
+        <v>18014.400000000001</v>
+      </c>
+      <c r="H3" s="5">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D4D520-27EC-4698-A208-66221AE4ABBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20031C24-A6B1-4F4C-86F8-475ABEFB5475}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="06,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="07,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,27 +31,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
+    <t>Симферополь</t>
   </si>
   <si>
-    <t>Сочи</t>
+    <t>09,10,26</t>
   </si>
   <si>
-    <t>08,10,26</t>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>10,10,26</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -86,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -139,11 +154,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -151,9 +248,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -166,13 +260,58 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -557,92 +696,221 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3">
-        <v>18.061</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7">
+        <v>17728.400000000001</v>
+      </c>
+      <c r="G1" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F2" s="3">
+        <v>17408.010000000002</v>
+      </c>
+      <c r="G2" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="4">
-        <v>18200.600000000006</v>
-      </c>
-      <c r="H1" s="5">
+      <c r="C3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="7">
+        <v>15784.580000000002</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>15605.36</v>
+      </c>
+      <c r="G4" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="7">
+        <v>17929.160000000003</v>
+      </c>
+      <c r="G5" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>6</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="11">
+        <v>14102.140000000001</v>
+      </c>
+      <c r="G6" s="12">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="8">
-        <v>18.026</v>
-      </c>
-      <c r="D2" s="9" t="s">
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="9">
-        <v>18150.86</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D7" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="15">
+        <v>3696.49</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="19">
+        <v>5582.8</v>
+      </c>
+      <c r="G8" s="20">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3">
-        <v>18</v>
-      </c>
-      <c r="D3" s="4" t="s">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4">
-        <v>18014.400000000001</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0.5</v>
+      <c r="D9" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="23">
+        <v>12198.04</v>
+      </c>
+      <c r="G9" s="24">
+        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20031C24-A6B1-4F4C-86F8-475ABEFB5475}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B472C2-1725-49A3-A9F9-A82A0FF19C64}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="07,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="08,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="8">
   <si>
     <t>КИ</t>
   </si>
@@ -39,16 +39,7 @@
     <t>Симферополь</t>
   </si>
   <si>
-    <t>09,10,26</t>
-  </si>
-  <si>
     <t>КСК</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>10,10,26</t>
   </si>
   <si>
     <t>Донецк</t>
@@ -57,10 +48,13 @@
     <t>НВ</t>
   </si>
   <si>
-    <t>Мариуполь</t>
+    <t>11,10,26</t>
   </si>
   <si>
-    <t>Луганск</t>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
   </si>
 </sst>
 </file>
@@ -119,51 +113,6 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -236,15 +185,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -254,7 +237,13 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -266,33 +255,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -300,6 +262,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -696,220 +670,171 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="13">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="7">
-        <v>17728.400000000001</v>
-      </c>
-      <c r="G1" s="8">
+      <c r="F1" s="2">
+        <v>15593.119999999999</v>
+      </c>
+      <c r="G1" s="3">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="14"/>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F2" s="5">
+        <v>2102.7200000000003</v>
+      </c>
+      <c r="G2" s="6">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="15">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="3">
-        <v>17408.010000000002</v>
-      </c>
-      <c r="G2" s="4">
-        <v>8.3333333333333329E-2</v>
+      <c r="F3" s="8">
+        <v>4158.96</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="7">
-        <v>15784.580000000002</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="D4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3">
-        <v>15605.36</v>
-      </c>
-      <c r="G4" s="4">
-        <v>4.1666666666666664E-2</v>
+      <c r="F4" s="19">
+        <v>8560.6200000000008</v>
+      </c>
+      <c r="G4" s="20">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="16"/>
+      <c r="B5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="7">
-        <v>17929.160000000003</v>
-      </c>
-      <c r="G5" s="8">
-        <v>4.1666666666666664E-2</v>
+      <c r="E5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="11">
+        <v>4960.67</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
-        <v>6</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="A6" s="13">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="11">
-        <v>14102.140000000001</v>
-      </c>
-      <c r="G6" s="12">
-        <v>0.41666666666666669</v>
+      <c r="E6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3111.66</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="15">
-        <v>3696.49</v>
-      </c>
-      <c r="G7" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="17">
-        <v>7</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="19">
-        <v>5582.8</v>
-      </c>
-      <c r="G8" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="23">
-        <v>12198.04</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0.45833333333333331</v>
+      <c r="E7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="5">
+        <v>14539.51</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B472C2-1725-49A3-A9F9-A82A0FF19C64}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AF7BDC-DFD0-45D6-86AB-54058924EA92}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="08,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="09,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'09,10,26'!$A$1:$G$23</definedName>
+  </definedNames>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="16">
   <si>
     <t>КИ</t>
   </si>
@@ -55,6 +58,30 @@
   </si>
   <si>
     <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>12,10,26</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>13,10,26</t>
+  </si>
+  <si>
+    <t>14,10,26</t>
+  </si>
+  <si>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -95,7 +122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -222,11 +249,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -264,21 +336,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -286,6 +343,57 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -670,171 +778,535 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="13">
+    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1">
+        <v>2</v>
+      </c>
+      <c r="C1">
+        <v>3</v>
+      </c>
+      <c r="D1">
+        <v>4</v>
+      </c>
+      <c r="E1">
+        <v>5</v>
+      </c>
+      <c r="F1">
+        <v>6</v>
+      </c>
+      <c r="G1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="27">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="8">
+        <v>5915.28</v>
+      </c>
+      <c r="G2" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="32"/>
+      <c r="B3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="14">
+        <v>5851.6800000000012</v>
+      </c>
+      <c r="G3" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="28"/>
+      <c r="B4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="11">
+        <v>6303.6200000000008</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16">
         <v>2</v>
       </c>
-      <c r="F1" s="2">
-        <v>15593.119999999999</v>
-      </c>
-      <c r="G1" s="3">
+      <c r="B5" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="18">
+        <v>14152.36</v>
+      </c>
+      <c r="G5" s="19">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="4" t="s">
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C6" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D6" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="22">
+        <v>17699.060000000001</v>
+      </c>
+      <c r="G6" s="23">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="29">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3466.6200000000003</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="30"/>
+      <c r="B8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="25">
+        <v>10412.210000000003</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="31"/>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="5">
+        <v>4034.2400000000007</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
         <v>5</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="B10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="22">
+        <v>17814.129999999997</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>6</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="18">
+        <v>16723.899999999998</v>
+      </c>
+      <c r="G11" s="19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
+        <v>7</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="22">
+        <v>11918.440000000002</v>
+      </c>
+      <c r="G12" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16">
+        <v>8</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="18">
+        <v>12260.56</v>
+      </c>
+      <c r="G13" s="19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="27">
+        <v>9</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2395.6799999999998</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="28"/>
+      <c r="B15" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="11">
+        <v>9928.64</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>10</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="5">
-        <v>2102.7200000000003</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="F16" s="18">
+        <v>17698.190000000002</v>
+      </c>
+      <c r="G16" s="19">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="15">
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="20">
+        <v>11</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="F17" s="22">
+        <v>15032.2</v>
+      </c>
+      <c r="G17" s="23">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16">
+        <v>12</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="18">
+        <v>17222.939999999999</v>
+      </c>
+      <c r="G18" s="19">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="20">
+        <v>13</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="22">
+        <v>17705.48</v>
+      </c>
+      <c r="G19" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="29">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2">
+        <v>5655.6</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="30"/>
+      <c r="B21" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="25">
+        <v>5778.7599999999993</v>
+      </c>
+      <c r="G21" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="31"/>
+      <c r="B22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="5">
+        <v>3639.96</v>
+      </c>
+      <c r="G22" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="20">
+        <v>15</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C23" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="8" t="s">
+      <c r="D23" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="8">
-        <v>4158.96</v>
-      </c>
-      <c r="G3" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="19">
-        <v>8560.6200000000008</v>
-      </c>
-      <c r="G4" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="11">
-        <v>4960.67</v>
-      </c>
-      <c r="G5" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="13">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3111.66</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
-      <c r="B7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="5">
-        <v>14539.51</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0.5</v>
+      <c r="F23" s="22">
+        <v>17023.750000000004</v>
+      </c>
+      <c r="G23" s="23">
+        <v>0.375</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A5"/>
+  <autoFilter ref="A1:G23" xr:uid="{8F8F73E8-CDB2-4B93-A6E8-C8043524029D}"/>
+  <mergeCells count="4">
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A7:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864C707E-AFF5-4CA4-AF23-19D7F87FCC97}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771A6FEA-11C2-4481-B09D-51C55F5DAD70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="13,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="14,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'14,10,26'!$A$1:$G$15</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="13">
   <si>
     <t>КИ</t>
   </si>
@@ -42,7 +45,34 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>15,10,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>16,10,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>17,10,26</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>Донецк</t>
   </si>
 </sst>
 </file>
@@ -83,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -136,11 +166,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -164,6 +313,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,59 +769,352 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1">
+        <v>3</v>
+      </c>
+      <c r="D1">
+        <v>4</v>
+      </c>
+      <c r="E1">
+        <v>5</v>
+      </c>
+      <c r="F1">
+        <v>6</v>
+      </c>
+      <c r="G1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3">
+        <v>17952.140000000003</v>
+      </c>
+      <c r="G2" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="27">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="C3" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="10">
+        <v>17629.28</v>
+      </c>
+      <c r="G3" s="11">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="28"/>
+      <c r="B4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="13">
+        <v>403.2</v>
+      </c>
+      <c r="G4" s="14">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="29">
+        <v>3</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3">
-        <v>18027.12</v>
-      </c>
-      <c r="G1" s="4">
+      <c r="F5" s="16">
+        <v>2000.8799999999999</v>
+      </c>
+      <c r="G5" s="17">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30"/>
+      <c r="B6" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="19">
+        <v>9704.36</v>
+      </c>
+      <c r="G6" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="7">
+        <v>17892.980000000003</v>
+      </c>
+      <c r="G7" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
+        <v>17602.579999999998</v>
+      </c>
+      <c r="G8" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="27">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="10">
+        <v>3281.2800000000007</v>
+      </c>
+      <c r="G9" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="31"/>
+      <c r="B10" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="22">
+        <v>5403.42</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="31"/>
+      <c r="B11" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="22">
+        <v>5817.8799999999992</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="28"/>
+      <c r="B12" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="13">
+        <v>3184.11</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="29">
+        <v>7</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="C13" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="D13" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="7">
-        <v>16571.16</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="F13" s="16">
+        <v>2549.6</v>
+      </c>
+      <c r="G13" s="17">
         <v>0.45833333333333331</v>
       </c>
     </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="32"/>
+      <c r="B14" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="25">
+        <v>4027.02</v>
+      </c>
+      <c r="G14" s="26">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
+      <c r="B15" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="19">
+        <v>11208.2</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G15" xr:uid="{3EBCD2A4-8E4F-45BE-B64F-6ADF6A91AE6A}"/>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771A6FEA-11C2-4481-B09D-51C55F5DAD70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139D3E73-4F3F-4082-9365-40997222E380}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="14,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="15,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'14,10,26'!$A$1:$G$15</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,23 +31,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
-  </si>
-  <si>
     <t>Симферополь</t>
   </si>
   <si>
-    <t>16,10,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
@@ -69,10 +57,10 @@
     <t>Мелитополь</t>
   </si>
   <si>
-    <t>Мариуполь</t>
-  </si>
-  <si>
-    <t>Донецк</t>
+    <t>18,10,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
   </si>
 </sst>
 </file>
@@ -113,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -167,19 +155,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -210,11 +185,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="medium">
@@ -226,8 +201,8 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
+      <right style="medium">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="medium">
@@ -236,52 +211,47 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -289,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -315,76 +285,58 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -769,351 +721,151 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1">
+      <c r="F1" s="7">
+        <v>14425.400000000001</v>
+      </c>
+      <c r="G1" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="19">
+        <v>2</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="15">
+        <v>15885.36</v>
+      </c>
+      <c r="G2" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="17">
+        <v>2092.3199999999997</v>
+      </c>
+      <c r="G3" s="18">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="23">
         <v>3</v>
       </c>
-      <c r="D1">
-        <v>4</v>
-      </c>
-      <c r="E1">
+      <c r="B4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F1">
-        <v>6</v>
-      </c>
-      <c r="G1">
+      <c r="F4" s="10">
+        <v>8166.6</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="C5" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D5" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3">
-        <v>17952.140000000003</v>
-      </c>
-      <c r="G2" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="27">
-        <v>2</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="10">
-        <v>17629.28</v>
-      </c>
-      <c r="G3" s="11">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
-      <c r="B4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="13">
-        <v>403.2</v>
-      </c>
-      <c r="G4" s="14">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="29">
-        <v>3</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="16">
-        <v>2000.8799999999999</v>
-      </c>
-      <c r="G5" s="17">
+      <c r="F5" s="12">
+        <v>9584.52</v>
+      </c>
+      <c r="G5" s="13">
         <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="B6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="19">
-        <v>9704.36</v>
-      </c>
-      <c r="G6" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>4</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="7" t="s">
+      <c r="E6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="7">
-        <v>17892.980000000003</v>
-      </c>
-      <c r="G7" s="8">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="3">
-        <v>17602.579999999998</v>
-      </c>
-      <c r="G8" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="27">
-        <v>6</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="10">
-        <v>3281.2800000000007</v>
-      </c>
-      <c r="G9" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="31"/>
-      <c r="B10" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="22">
-        <v>5403.42</v>
-      </c>
-      <c r="G10" s="23">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="31"/>
-      <c r="B11" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="22">
-        <v>5817.8799999999992</v>
-      </c>
-      <c r="G11" s="23">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="13">
-        <v>3184.11</v>
-      </c>
-      <c r="G12" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="29">
-        <v>7</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="16">
-        <v>2549.6</v>
-      </c>
-      <c r="G13" s="17">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="32"/>
-      <c r="B14" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="25">
-        <v>4027.02</v>
-      </c>
-      <c r="G14" s="26">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="19">
-        <v>11208.2</v>
-      </c>
-      <c r="G15" s="20">
+      <c r="F6" s="3">
+        <v>17858.260000000002</v>
+      </c>
+      <c r="G6" s="4">
         <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G15" xr:uid="{3EBCD2A4-8E4F-45BE-B64F-6ADF6A91AE6A}"/>
-  <mergeCells count="4">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A13:A15"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139D3E73-4F3F-4082-9365-40997222E380}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF37D2A6-4FA9-4234-81F1-FC1BE23F8565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="15,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="16,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'16,10,26'!$A$1:$G$25</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="14">
   <si>
     <t>КИ</t>
   </si>
@@ -51,16 +48,28 @@
     <t>НВ</t>
   </si>
   <si>
-    <t>17,10,26</t>
-  </si>
-  <si>
     <t>Мелитополь</t>
   </si>
   <si>
-    <t>18,10,26</t>
+    <t>Бердянск</t>
   </si>
   <si>
-    <t>Бердянск</t>
+    <t>19,10,26</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>20,10,26</t>
+  </si>
+  <si>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -101,7 +110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -220,6 +229,41 @@
       <top style="medium">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -232,24 +276,7 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -259,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -315,11 +342,20 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -327,16 +363,25 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -721,86 +766,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G6"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5">
+    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1">
+        <v>2</v>
+      </c>
+      <c r="C1">
+        <v>3</v>
+      </c>
+      <c r="D1">
+        <v>4</v>
+      </c>
+      <c r="E1">
+        <v>5</v>
+      </c>
+      <c r="F1">
+        <v>6</v>
+      </c>
+      <c r="G1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="B2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="7">
+        <v>17667.159999999996</v>
+      </c>
+      <c r="G2" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="7">
-        <v>14425.400000000001</v>
-      </c>
-      <c r="G1" s="8">
+      <c r="F3" s="3">
+        <v>15376.039999999999</v>
+      </c>
+      <c r="G3" s="4">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="19">
-        <v>2</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="15">
-        <v>15885.36</v>
-      </c>
-      <c r="G2" s="16">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="17">
-        <v>2092.3199999999997</v>
-      </c>
-      <c r="G3" s="18">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
     <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="23">
+      <c r="A4" s="27">
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>0</v>
@@ -812,60 +860,492 @@
         <v>5</v>
       </c>
       <c r="F4" s="10">
-        <v>8166.6</v>
+        <v>8685.2199999999993</v>
       </c>
       <c r="G4" s="11">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25" t="s">
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="32"/>
+      <c r="B5" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="20">
+        <v>4929.2800000000007</v>
+      </c>
+      <c r="G5" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28"/>
+      <c r="B6" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="12">
+        <v>4350.8700000000008</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="29">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="15">
+        <v>12140.419999999998</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="31"/>
+      <c r="B8" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="17">
+        <v>5715.4</v>
+      </c>
+      <c r="G8" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>17436.09</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="29">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C10" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="15">
+        <v>5844.24</v>
+      </c>
+      <c r="G10" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="30"/>
+      <c r="B11" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="25">
+        <v>7673.0800000000008</v>
+      </c>
+      <c r="G11" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="31"/>
+      <c r="B12" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="17">
+        <v>1425.48</v>
+      </c>
+      <c r="G12" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="27">
+        <v>7</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="10">
+        <v>6281.8</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="28"/>
+      <c r="B14" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="12">
+        <v>7074.4800000000005</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>12984.160000000002</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="7">
+        <v>12372.38</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>10</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="12">
-        <v>9584.52</v>
-      </c>
-      <c r="G5" s="13">
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>17768.859999999997</v>
+      </c>
+      <c r="G17" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>11</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F18" s="7">
+        <v>17738.560000000001</v>
+      </c>
+      <c r="G18" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="29">
+        <v>12</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="15">
+        <v>12486.280000000002</v>
+      </c>
+      <c r="G19" s="16">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="30"/>
+      <c r="B20" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="25">
+        <v>4495.2</v>
+      </c>
+      <c r="G20" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="31"/>
+      <c r="B21" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="17">
+        <v>1033.2</v>
+      </c>
+      <c r="G21" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>13</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="7">
+        <v>17765.47</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>14</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3">
-        <v>17858.260000000002</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.45833333333333331</v>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>17182.5</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="27">
+        <v>15</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="10">
+        <v>9987.9599999999991</v>
+      </c>
+      <c r="G24" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28"/>
+      <c r="B25" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="12">
+        <v>4849.8</v>
+      </c>
+      <c r="G25" s="13">
+        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
+  <autoFilter ref="A1:G25" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="НВ"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="6">
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A10:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F364A25D-029C-4326-AFDF-2A32FFE11811}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31F9431-F879-4C82-BB3C-3716C651655C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="19,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="20,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +42,7 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>21,10,26</t>
+    <t>22,10,26</t>
   </si>
 </sst>
 </file>
@@ -63,7 +63,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -76,8 +76,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -86,16 +92,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -104,13 +110,13 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -119,51 +125,14 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -173,28 +142,28 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -582,58 +551,56 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="8.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="7">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2">
-        <v>2851.34</v>
-      </c>
-      <c r="G1" s="3">
-        <v>0.5</v>
+      <c r="F1" s="3">
+        <v>18087.219999999998</v>
+      </c>
+      <c r="G1" s="4">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
+      <c r="A2" s="5">
+        <v>2</v>
+      </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
-        <v>11341.109999999999</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0.5</v>
+      <c r="F2" s="7">
+        <v>18094.03</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31F9431-F879-4C82-BB3C-3716C651655C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587D0843-A4D0-4A1F-AB57-745F1E4C4E5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="21,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,18 +31,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
-  </si>
-  <si>
-    <t>22,10,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>23,10,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>24,10,26</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Донецк</t>
   </si>
 </sst>
 </file>
@@ -548,9 +563,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -559,22 +575,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
       <c r="F1" s="3">
-        <v>18087.219999999998</v>
+        <v>17790.560000000001</v>
       </c>
       <c r="G1" s="4">
-        <v>0.41666666666666669</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -582,21 +598,113 @@
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="E2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="7">
+        <v>14388.84</v>
+      </c>
+      <c r="G2" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F3" s="3">
+        <v>17766.98</v>
+      </c>
+      <c r="G3" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="7">
-        <v>18094.03</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="C4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="7">
+        <v>17806.7</v>
+      </c>
+      <c r="G4" s="8">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="3">
+        <v>17826.310000000001</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>6</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="7">
+        <v>17746.12</v>
+      </c>
+      <c r="G6" s="8">
         <v>0.45833333333333331</v>
       </c>
     </row>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587D0843-A4D0-4A1F-AB57-745F1E4C4E5E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9568540F-B105-499C-AAB9-AADF751ECB60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="21,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="22,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="12">
   <si>
     <t>КИ</t>
   </si>
@@ -39,25 +39,34 @@
     <t>Симферополь</t>
   </si>
   <si>
-    <t>23,10,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
     <t>24,10,26</t>
   </si>
   <si>
-    <t>Луганск</t>
-  </si>
-  <si>
     <t>НВ</t>
   </si>
   <si>
     <t>Донецк</t>
+  </si>
+  <si>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>25,10,26</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -98,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -151,24 +160,131 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -179,6 +295,66 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -563,152 +739,350 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="7">
+        <v>4177.38</v>
+      </c>
+      <c r="G1" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="11">
+        <v>7727.94</v>
+      </c>
+      <c r="G2" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="15">
+        <v>5420.85</v>
+      </c>
+      <c r="G3" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3">
+        <v>3942.1199999999994</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3">
-        <v>17790.560000000001</v>
-      </c>
-      <c r="G1" s="4">
+      <c r="F5" s="7">
+        <v>15815.860000000002</v>
+      </c>
+      <c r="G5" s="8">
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="F6" s="15">
+        <v>2536.36</v>
+      </c>
+      <c r="G6" s="16">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>15278.58</v>
+      </c>
+      <c r="G7" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="7">
+        <v>4320.4799999999996</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="7">
-        <v>14388.84</v>
-      </c>
-      <c r="G2" s="8">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="F9" s="11">
+        <v>3725.2400000000002</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="11">
+        <v>4396.2</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="15">
+        <v>5054.7400000000016</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="17">
+        <v>6</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="3">
-        <v>17766.98</v>
-      </c>
-      <c r="G3" s="4">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="C12" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="s">
+      <c r="F12" s="19">
+        <v>12590.420000000002</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="7">
-        <v>17806.7</v>
-      </c>
-      <c r="G4" s="8">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="3">
-        <v>17826.310000000001</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>6</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="C13" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="23">
+        <v>5020.8</v>
+      </c>
+      <c r="G13" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="5">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="7">
+        <v>8925.9599999999991</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="7">
-        <v>17746.12</v>
-      </c>
-      <c r="G6" s="8">
-        <v>0.45833333333333331</v>
+      <c r="C15" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="15">
+        <v>8807.24</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9568540F-B105-499C-AAB9-AADF751ECB60}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60F3D45-A128-42B5-975F-F2C9BB5D16F4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="22,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="23,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'23,10,26'!$A$1:$G$27</definedName>
+  </definedNames>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="15">
   <si>
     <t>КИ</t>
   </si>
@@ -42,9 +45,6 @@
     <t>КСК</t>
   </si>
   <si>
-    <t>24,10,26</t>
-  </si>
-  <si>
     <t>НВ</t>
   </si>
   <si>
@@ -67,6 +67,18 @@
   </si>
   <si>
     <t>Сочи</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>26,10,26</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>27,10,26</t>
   </si>
 </sst>
 </file>
@@ -283,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -297,9 +309,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -309,9 +318,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -321,9 +327,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -333,18 +336,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -355,6 +346,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -739,349 +766,623 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="5">
+    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1">
+        <v>2</v>
+      </c>
+      <c r="C1">
+        <v>3</v>
+      </c>
+      <c r="D1">
+        <v>4</v>
+      </c>
+      <c r="E1">
+        <v>5</v>
+      </c>
+      <c r="F1">
+        <v>6</v>
+      </c>
+      <c r="G1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="7">
-        <v>4177.38</v>
-      </c>
-      <c r="G1" s="8">
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>14771.439999999999</v>
+      </c>
+      <c r="G2" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="20">
+        <v>3897.8999999999996</v>
+      </c>
+      <c r="G3" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="25">
+        <v>3</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="23">
+        <v>15526.1</v>
+      </c>
+      <c r="G4" s="24">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="26"/>
+      <c r="B5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="16">
+        <v>2352</v>
+      </c>
+      <c r="G5" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="27">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="6">
+        <v>7079.1399999999994</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="29"/>
+      <c r="B7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="9">
+        <v>2964.2200000000003</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="29"/>
+      <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="9">
+        <v>5919.58</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="28"/>
+      <c r="B9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="12">
+        <v>1998.1400000000003</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>5</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="16">
+        <v>16677.73</v>
+      </c>
+      <c r="G10" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
+        <v>6</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="20">
+        <v>17379.25</v>
+      </c>
+      <c r="G11" s="21">
         <v>0.5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10" t="s">
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="25">
+        <v>7</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="11">
-        <v>7727.94</v>
-      </c>
-      <c r="G2" s="12">
+      <c r="D12" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="23">
+        <v>1543.4800000000002</v>
+      </c>
+      <c r="G12" s="24">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="25"/>
+      <c r="B13" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="23">
+        <v>7117.6800000000012</v>
+      </c>
+      <c r="G13" s="24">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26"/>
+      <c r="B14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="16">
+        <v>6229.5600000000013</v>
+      </c>
+      <c r="G14" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18">
+        <v>8</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="20">
+        <v>2914.3199999999997</v>
+      </c>
+      <c r="G15" s="21">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <v>9</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="16">
+        <v>17826.480000000003</v>
+      </c>
+      <c r="G16" s="17">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18">
+        <v>10</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F17" s="20">
+        <v>14930.519999999999</v>
+      </c>
+      <c r="G17" s="21">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="25">
+        <v>11</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="23">
+        <v>6391.6800000000012</v>
+      </c>
+      <c r="G18" s="24">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="26"/>
+      <c r="B19" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="16">
+        <v>11337.57</v>
+      </c>
+      <c r="G19" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="27">
+        <v>12</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="6">
+        <v>5063.2</v>
+      </c>
+      <c r="G20" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28"/>
+      <c r="B21" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="12">
+        <v>12699.64</v>
+      </c>
+      <c r="G21" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="25">
+        <v>13</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="23">
+        <v>12486.280000000002</v>
+      </c>
+      <c r="G22" s="24">
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14" t="s">
+    <row r="23" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="25"/>
+      <c r="B23" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F23" s="23">
+        <v>4495.2</v>
+      </c>
+      <c r="G23" s="24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="26"/>
+      <c r="B24" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="16">
+        <v>1012.8000000000001</v>
+      </c>
+      <c r="G24" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
+        <v>14</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="15">
-        <v>5420.85</v>
-      </c>
-      <c r="G3" s="16">
+      <c r="D25" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="20">
+        <v>3201.12</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <v>15</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="16">
+        <v>12427.880000000001</v>
+      </c>
+      <c r="G26" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <v>16</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="20">
+        <v>12988.240000000002</v>
+      </c>
+      <c r="G27" s="21">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="3">
-        <v>3942.1199999999994</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="7">
-        <v>15815.860000000002</v>
-      </c>
-      <c r="G5" s="8">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="15">
-        <v>2536.36</v>
-      </c>
-      <c r="G6" s="16">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>4</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>15278.58</v>
-      </c>
-      <c r="G7" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="7">
-        <v>4320.4799999999996</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="11">
-        <v>3725.2400000000002</v>
-      </c>
-      <c r="G9" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="11">
-        <v>4396.2</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="15">
-        <v>5054.7400000000016</v>
-      </c>
-      <c r="G11" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="17">
-        <v>6</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="19">
-        <v>12590.420000000002</v>
-      </c>
-      <c r="G12" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="23">
-        <v>5020.8</v>
-      </c>
-      <c r="G13" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
-        <v>7</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="7">
-        <v>8925.9599999999991</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="15">
-        <v>8807.24</v>
-      </c>
-      <c r="G15" s="16">
-        <v>0.5</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
+  <autoFilter ref="A1:G27" xr:uid="{5A1FB940-84AD-4FCC-B9DD-5C3E3FA6A52D}"/>
+  <mergeCells count="6">
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A12:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E49505C-24FC-4B70-B602-01937AC7DE32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E1F8AA-FD40-4D5C-B651-D500CC3725E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="27,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="28,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'28,10,26'!$A$1:$G$9</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
@@ -48,13 +51,19 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>ЗПФ</t>
+    <t>30,10,26</t>
   </si>
   <si>
-    <t>29,10,26</t>
+    <t>Симферополь</t>
   </si>
   <si>
-    <t>30,10,26</t>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>31,10,26</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
@@ -95,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -148,11 +157,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -176,6 +304,66 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -560,83 +748,220 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1">
+        <v>2</v>
+      </c>
+      <c r="C1">
+        <v>3</v>
+      </c>
+      <c r="D1">
         <v>4</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1">
+        <v>5</v>
+      </c>
+      <c r="F1">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3">
-        <v>18135.18</v>
-      </c>
-      <c r="G1" s="4">
-        <v>0.41666666666666669</v>
+      <c r="G1">
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F2" s="7">
-        <v>18094.650000000001</v>
+        <v>17709.62</v>
       </c>
       <c r="G2" s="8">
-        <v>0.45833333333333331</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="3">
+        <v>17609.28</v>
+      </c>
+      <c r="G3" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="7">
+        <v>17642.300000000003</v>
+      </c>
+      <c r="G4" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="24">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2616.5219999999999</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25"/>
+      <c r="B6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C6" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13">
+        <v>15593.58</v>
+      </c>
+      <c r="G6" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="26">
         <v>5</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="B7" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="3">
-        <v>14775.6</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.41666666666666669</v>
+      <c r="F7" s="16">
+        <v>5115.1600000000008</v>
+      </c>
+      <c r="G7" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="27"/>
+      <c r="B8" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="19">
+        <v>12284.33</v>
+      </c>
+      <c r="G8" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="28"/>
+      <c r="B9" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="22">
+        <v>327.60000000000008</v>
+      </c>
+      <c r="G9" s="23">
+        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G9" xr:uid="{F084B775-43AD-4A8F-B1D4-43CB0FABB983}"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E1F8AA-FD40-4D5C-B651-D500CC3725E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59917B13-7053-4BCD-A13F-841FDA6A0E47}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="28,10,26" sheetId="101" r:id="rId1"/>
+    <sheet name="29,10,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'28,10,26'!$A$1:$G$9</definedName>
-  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="9">
   <si>
     <t>КИ</t>
   </si>
@@ -45,25 +42,22 @@
     <t>Донецк</t>
   </si>
   <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
-  </si>
-  <si>
-    <t>30,10,26</t>
-  </si>
-  <si>
     <t>Симферополь</t>
   </si>
   <si>
     <t>КСК</t>
   </si>
   <si>
-    <t>31,10,26</t>
+    <t>01,11,26</t>
   </si>
   <si>
-    <t>Луганск</t>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
   </si>
 </sst>
 </file>
@@ -333,15 +327,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -360,10 +345,19 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -748,219 +742,172 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3">
+        <v>17820.980000000003</v>
+      </c>
+      <c r="G1" s="4">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="23">
         <v>2</v>
       </c>
-      <c r="C1">
+      <c r="B2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D1">
+      <c r="C2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E1">
-        <v>5</v>
-      </c>
-      <c r="F1">
-        <v>6</v>
-      </c>
-      <c r="G1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="7">
-        <v>17709.62</v>
-      </c>
-      <c r="G2" s="8">
-        <v>4.1666666666666664E-2</v>
+      <c r="F2" s="16">
+        <v>15649.460000000003</v>
+      </c>
+      <c r="G2" s="17">
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="24"/>
+      <c r="B3" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="19">
+        <v>2267.64</v>
+      </c>
+      <c r="G3" s="20">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="21">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="3">
-        <v>17609.28</v>
-      </c>
-      <c r="G3" s="4">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="7">
-        <v>17642.300000000003</v>
-      </c>
-      <c r="G4" s="8">
-        <v>4.1666666666666664E-2</v>
+      <c r="E4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="10">
+        <v>3282.98</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="24">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="A5" s="25"/>
+      <c r="B5" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>2616.5219999999999</v>
-      </c>
-      <c r="G5" s="11">
+      <c r="D5" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="27">
+        <v>12235.69</v>
+      </c>
+      <c r="G5" s="28">
         <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="25"/>
+      <c r="A6" s="22"/>
       <c r="B6" s="12" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>1</v>
       </c>
       <c r="F6" s="13">
-        <v>15593.58</v>
+        <v>2387.7000000000003</v>
       </c>
       <c r="G6" s="14">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="26">
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="16">
-        <v>5115.1600000000008</v>
-      </c>
-      <c r="G7" s="17">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="19">
-        <v>12284.33</v>
-      </c>
-      <c r="G8" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="22">
-        <v>327.60000000000008</v>
-      </c>
-      <c r="G9" s="23">
+      <c r="F7" s="7">
+        <v>17737.54</v>
+      </c>
+      <c r="G7" s="8">
         <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{F084B775-43AD-4A8F-B1D4-43CB0FABB983}"/>
   <mergeCells count="2">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
